--- a/physician_forms/002_medical_intake_form--physician_forms.xlsx
+++ b/physician_forms/002_medical_intake_form--physician_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -799,7 +799,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
@@ -1104,12 +1104,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>nephrology</t>
+          <t>ophthalmology</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Nephrology</t>
+          <t>Ophthalmology</t>
         </is>
       </c>
     </row>
@@ -1121,12 +1121,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>neurology</t>
+          <t>orthopedic</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Neurology</t>
+          <t>Orthopedic</t>
         </is>
       </c>
     </row>
@@ -1138,12 +1138,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>obstetrics_and_gynecology</t>
+          <t>pathology</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Obstetrics and Gynecology</t>
+          <t>Pathology</t>
         </is>
       </c>
     </row>
@@ -1155,12 +1155,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ophthalmology</t>
+          <t>radiology</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Ophthalmology</t>
+          <t>Radiology</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1172,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>orthopedic</t>
+          <t>rheumatology</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Orthopedic</t>
+          <t>Rheumatology</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>pathology</t>
+          <t>urology</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Pathology</t>
+          <t>Urology</t>
         </is>
       </c>
     </row>
@@ -1206,12 +1206,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>pediatrics</t>
+          <t>general_medicine</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Pediatrics</t>
+          <t>General Medicine</t>
         </is>
       </c>
     </row>
@@ -1223,97 +1223,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>radiology</t>
+          <t>oncology</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Radiology</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>medical_specialties_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>rheumatology</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Rheumatology</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>medical_specialties_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>urology</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Urology</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>medical_specialties_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>general_medicine</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>General Medicine</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>medical_specialties_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>oncology</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
           <t>Oncology</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>medical_specialties_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>cardiology</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Cardiology</t>
         </is>
       </c>
     </row>
